--- a/IS453_Multicollinearity_Feature_Report.xlsx
+++ b/IS453_Multicollinearity_Feature_Report.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Multicollinearity Analysis" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Feature Extraction Proposals" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Multicollinearity Analysis" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Extraction Proposals" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -627,7 +627,7 @@
         <v>37.93</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.0521</v>
+        <v>0.0505</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
         <v>37.78</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>0.0418</v>
+        <v>0.0871</v>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
@@ -710,10 +710,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C6" s="5" t="n">
+        <v>0.0254</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
@@ -904,7 +902,7 @@
         <v>10.57</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>0.0791</v>
+        <v>0.0274</v>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
@@ -945,7 +943,7 @@
         <v>10.6</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.0832</v>
+        <v>0.0279</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
@@ -993,7 +991,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.1243</v>
+        <v>0.1244</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
@@ -1034,7 +1032,7 @@
         <v>8.449999999999999</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0.0987</v>
+        <v>0.0801</v>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
@@ -1077,7 +1075,7 @@
         <v>8.449999999999999</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.0612</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
@@ -1127,7 +1125,7 @@
         <v>8.23</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.0743</v>
+        <v>0</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
@@ -1168,7 +1166,7 @@
         <v>6.56</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>0.0441</v>
+        <v>0</v>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
@@ -1217,10 +1215,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C21" s="9" t="n">
+        <v>0.0113</v>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
@@ -1262,10 +1258,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C22" s="5" t="n">
+        <v>0.0113</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
@@ -1361,10 +1355,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C25" s="9" t="n">
+        <v>0.0287</v>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
@@ -1406,10 +1398,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C26" s="5" t="n">
+        <v>0.028</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
@@ -1458,10 +1448,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C28" s="5" t="n">
+        <v>0.0007</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
@@ -1503,10 +1491,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C29" s="9" t="n">
+        <v>0.0007</v>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
@@ -1548,10 +1534,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C30" s="5" t="n">
+        <v>0.0049</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
@@ -1595,10 +1579,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C31" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
@@ -1696,10 +1678,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C34" s="5" t="n">
+        <v>0.0458</v>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
@@ -1741,10 +1721,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C35" s="9" t="n">
+        <v>0.0438</v>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
@@ -1786,10 +1764,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C36" s="5" t="n">
+        <v>0.0555</v>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
@@ -1887,10 +1863,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C39" s="9" t="n">
+        <v>0.0115</v>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
@@ -1934,10 +1908,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C40" s="5" t="n">
+        <v>0.0115</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
@@ -1988,10 +1960,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C42" s="5" t="n">
+        <v>0.0175</v>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
@@ -2035,10 +2005,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C43" s="9" t="n">
+        <v>0.0196</v>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
@@ -2082,10 +2050,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C44" s="5" t="n">
+        <v>0.0182</v>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
@@ -2136,10 +2102,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C46" s="5" t="n">
+        <v>0.0134</v>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
@@ -2183,10 +2147,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C47" s="9" t="n">
+        <v>0.0129</v>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
@@ -2230,10 +2192,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C48" s="5" t="n">
+        <v>0.014</v>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
@@ -2331,10 +2291,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C51" s="9" t="n">
+        <v>0.0113</v>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
@@ -2378,10 +2336,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C52" s="5" t="n">
+        <v>0.0113</v>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
@@ -2425,10 +2381,8 @@
           <t>Not in top 30</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C53" s="9" t="n">
+        <v>0.0113</v>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
